--- a/Horarios/Colectivos/136-Rapido/DomingoPrimeraJunta.xlsx
+++ b/Horarios/Colectivos/136-Rapido/DomingoPrimeraJunta.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Horarios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Horarios" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>739_295702-1</t>
+          <t>739_295691-1</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -519,7 +519,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>739_295703-1</t>
+          <t>739_295692-1</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -540,7 +540,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>739_295704-1</t>
+          <t>739_295693-1</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -561,7 +561,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>739_295705-1</t>
+          <t>739_295694-1</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -582,7 +582,7 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>739_295706-1</t>
+          <t>739_295695-1</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -603,7 +603,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>739_295707-1</t>
+          <t>739_295696-1</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -624,7 +624,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>739_295708-1</t>
+          <t>739_295697-1</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -645,7 +645,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>739_295709-1</t>
+          <t>739_295698-1</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -666,7 +666,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>739_295710-1</t>
+          <t>739_295699-1</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -687,7 +687,7 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>739_295711-1</t>
+          <t>739_295700-1</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -708,7 +708,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>739_295712-1</t>
+          <t>739_295701-1</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -729,7 +729,7 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>739_295713-1</t>
+          <t>739_295702-1</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -748,7 +748,7 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>739_295714-1</t>
+          <t>739_295703-1</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -769,7 +769,7 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>739_295715-1</t>
+          <t>739_295704-1</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -788,7 +788,7 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>739_295716-1</t>
+          <t>739_295705-1</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
